--- a/TELEMETRYadcCLOCK/project/Efficiency.xlsx
+++ b/TELEMETRYadcCLOCK/project/Efficiency.xlsx
@@ -9,33 +9,32 @@
   <sheets>
     <sheet name="No Zero Net" sheetId="1" r:id="rId1"/>
     <sheet name="Validate no &quot;text&quot; in Datamaps" sheetId="2" r:id="rId2"/>
-    <sheet name="Missing Bio Symbol Files" sheetId="3" r:id="rId3"/>
-    <sheet name="Missing Nets" sheetId="4" r:id="rId4"/>
-    <sheet name="Shorted Inputs" sheetId="5" r:id="rId5"/>
-    <sheet name="Shorted Outputs" sheetId="6" r:id="rId6"/>
-    <sheet name="Floating Inputs" sheetId="7" r:id="rId7"/>
-    <sheet name="Floating Outputs" sheetId="8" r:id="rId8"/>
-    <sheet name="No Connects - Outputs" sheetId="9" r:id="rId9"/>
-    <sheet name="No Connects - Inputs" sheetId="10" r:id="rId10"/>
-    <sheet name="Mixed Mode Conflicts" sheetId="11" r:id="rId11"/>
-    <sheet name="Ring Core IO check report" sheetId="12" r:id="rId12"/>
-    <sheet name="D to A Tree" sheetId="13" r:id="rId13"/>
-    <sheet name="Symbol Length Exceed Max" sheetId="14" r:id="rId14"/>
-    <sheet name="Cell Length Exceed Max 50" sheetId="15" r:id="rId15"/>
-    <sheet name="All Nestos have Verilog File" sheetId="16" r:id="rId16"/>
-    <sheet name="Zero Length Verilog Files" sheetId="17" r:id="rId17"/>
-    <sheet name="Verilog Checker" sheetId="18" r:id="rId18"/>
-    <sheet name="DRM Efficiency" sheetId="19" r:id="rId19"/>
-    <sheet name="DRM Efficiency Summary" sheetId="20" r:id="rId20"/>
-    <sheet name="DFT Efficiency" sheetId="21" r:id="rId21"/>
-    <sheet name="DFM Efficiency Summary" sheetId="22" r:id="rId22"/>
+    <sheet name="Missing Nets" sheetId="3" r:id="rId3"/>
+    <sheet name="Shorted Inputs" sheetId="4" r:id="rId4"/>
+    <sheet name="Shorted Outputs" sheetId="5" r:id="rId5"/>
+    <sheet name="Floating Inputs" sheetId="6" r:id="rId6"/>
+    <sheet name="Floating Outputs" sheetId="7" r:id="rId7"/>
+    <sheet name="No Connects - Outputs" sheetId="8" r:id="rId8"/>
+    <sheet name="No Connects - Inputs" sheetId="9" r:id="rId9"/>
+    <sheet name="Mixed Mode Conflicts" sheetId="10" r:id="rId10"/>
+    <sheet name="Ring Core IO check report" sheetId="11" r:id="rId11"/>
+    <sheet name="D to A Tree" sheetId="12" r:id="rId12"/>
+    <sheet name="Symbol Length Exceed Max" sheetId="13" r:id="rId13"/>
+    <sheet name="Cell Length Exceed Max 50" sheetId="14" r:id="rId14"/>
+    <sheet name="All Nestos have Verilog File" sheetId="15" r:id="rId15"/>
+    <sheet name="Zero Length Verilog Files" sheetId="16" r:id="rId16"/>
+    <sheet name="Verilog Checker" sheetId="17" r:id="rId17"/>
+    <sheet name="DRM Efficiency" sheetId="18" r:id="rId18"/>
+    <sheet name="DRM Efficiency Summary" sheetId="19" r:id="rId19"/>
+    <sheet name="DFT Efficiency" sheetId="20" r:id="rId20"/>
+    <sheet name="DFM Efficiency Summary" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="62">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -64,16 +63,13 @@
     <t>Xdatamap1 (datamap.function) missing expected field datamap_function_2</t>
   </si>
   <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>No missing bio or symbol files...</t>
-  </si>
-  <si>
     <t>Missing Nets</t>
   </si>
   <si>
-    <t>All symbols have nets.</t>
+    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+  </si>
+  <si>
+    <t>Xoscillator1,CELREF</t>
   </si>
   <si>
     <t>Shorted Inputs</t>
@@ -91,13 +87,7 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>(!!! MUST FIX !!! - not allowed)</t>
-  </si>
-  <si>
-    <t>XCLOCK</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CELREF84329(CELREF84329)</t>
+    <t>No Floating Input Nets found.</t>
   </si>
   <si>
     <t>Floating Outputs</t>
@@ -110,9 +100,6 @@
   </si>
   <si>
     <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>CELREF84329 - {"path": "XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CELREF84329", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -602,30 +589,75 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -637,292 +669,247 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A48"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
         <v>59</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -967,6 +954,26 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -977,57 +984,12 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1037,7 +999,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1055,6 +1017,16 @@
         <v>10</v>
       </c>
     </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1067,7 +1039,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1077,7 +1049,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1092,7 +1064,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1102,7 +1074,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1117,7 +1089,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1127,7 +1099,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1137,12 +1109,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>17</v>
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1152,27 +1124,37 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1185,31 +1167,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TELEMETRYadcCLOCK/project/Efficiency.xlsx
+++ b/TELEMETRYadcCLOCK/project/Efficiency.xlsx
@@ -10,31 +10,30 @@
     <sheet name="No Zero Net" sheetId="1" r:id="rId1"/>
     <sheet name="Validate no &quot;text&quot; in Datamaps" sheetId="2" r:id="rId2"/>
     <sheet name="Missing Nets" sheetId="3" r:id="rId3"/>
-    <sheet name="Shorted Inputs" sheetId="4" r:id="rId4"/>
-    <sheet name="Shorted Outputs" sheetId="5" r:id="rId5"/>
-    <sheet name="Floating Inputs" sheetId="6" r:id="rId6"/>
-    <sheet name="Floating Outputs" sheetId="7" r:id="rId7"/>
-    <sheet name="No Connects - Outputs" sheetId="8" r:id="rId8"/>
-    <sheet name="No Connects - Inputs" sheetId="9" r:id="rId9"/>
-    <sheet name="Mixed Mode Conflicts" sheetId="10" r:id="rId10"/>
-    <sheet name="Ring Core IO check report" sheetId="11" r:id="rId11"/>
-    <sheet name="D to A Tree" sheetId="12" r:id="rId12"/>
-    <sheet name="Symbol Length Exceed Max" sheetId="13" r:id="rId13"/>
-    <sheet name="Cell Length Exceed Max 50" sheetId="14" r:id="rId14"/>
-    <sheet name="All Nestos have Verilog File" sheetId="15" r:id="rId15"/>
-    <sheet name="Zero Length Verilog Files" sheetId="16" r:id="rId16"/>
-    <sheet name="Verilog Checker" sheetId="17" r:id="rId17"/>
-    <sheet name="DRM Efficiency" sheetId="18" r:id="rId18"/>
-    <sheet name="DRM Efficiency Summary" sheetId="19" r:id="rId19"/>
-    <sheet name="DFT Efficiency" sheetId="20" r:id="rId20"/>
-    <sheet name="DFM Efficiency Summary" sheetId="21" r:id="rId21"/>
+    <sheet name="Shorted Nets" sheetId="4" r:id="rId4"/>
+    <sheet name="Floating Inputs" sheetId="5" r:id="rId5"/>
+    <sheet name="Floating Outputs" sheetId="6" r:id="rId6"/>
+    <sheet name="No Connects - Customer" sheetId="7" r:id="rId7"/>
+    <sheet name="No Connects - Celera" sheetId="8" r:id="rId8"/>
+    <sheet name="Mixed Mode Conflicts" sheetId="9" r:id="rId9"/>
+    <sheet name="Ring Core IO check report" sheetId="10" r:id="rId10"/>
+    <sheet name="D to A Tree" sheetId="11" r:id="rId11"/>
+    <sheet name="Symbol Length Exceed Max" sheetId="12" r:id="rId12"/>
+    <sheet name="Cell Length Exceed Max 50" sheetId="13" r:id="rId13"/>
+    <sheet name="All Nestos have Verilog File" sheetId="14" r:id="rId14"/>
+    <sheet name="Zero Length Verilog Files" sheetId="15" r:id="rId15"/>
+    <sheet name="Verilog Checker" sheetId="16" r:id="rId16"/>
+    <sheet name="DRM Efficiency" sheetId="17" r:id="rId17"/>
+    <sheet name="DRM Efficiency Summary" sheetId="18" r:id="rId18"/>
+    <sheet name="DFT Efficiency" sheetId="19" r:id="rId19"/>
+    <sheet name="DFM Efficiency Summary" sheetId="20" r:id="rId20"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="64">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -72,34 +71,40 @@
     <t>Xoscillator1,CELREF</t>
   </si>
   <si>
-    <t>Shorted Inputs</t>
-  </si>
-  <si>
-    <t>No Shorted Input Nets found.</t>
-  </si>
-  <si>
-    <t>Shorted Outputs</t>
-  </si>
-  <si>
-    <t>No Shorted Output Nets found.</t>
+    <t>Shorted Nets</t>
+  </si>
+  <si>
+    <t>No Shorted Nets found.</t>
   </si>
   <si>
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XCLOCK,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.dft_clock(dft_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.fault_adcclock(fault_adcclock)</t>
+  </si>
+  <si>
+    <t>Floating pin Xoscillator1.global_oscillatorring(tl0)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>No Floating Output Nets found.</t>
-  </si>
-  <si>
-    <t>No Connects - Outputs</t>
-  </si>
-  <si>
-    <t>No Connects - Inputs</t>
+    <t>No Connects - Customer</t>
+  </si>
+  <si>
+    <t>No Connects - Celera</t>
+  </si>
+  <si>
+    <t>XU1.pulse net: XUADCCLOCKstartup_no_dft_noconn_pulse io: output</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -589,32 +594,12 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -629,7 +614,27 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -644,7 +649,67 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -657,214 +722,154 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -874,42 +879,42 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -954,42 +959,22 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1059,7 +1044,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1077,6 +1062,31 @@
         <v>15</v>
       </c>
     </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1084,17 +1094,17 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -1102,6 +1112,21 @@
         <v>17</v>
       </c>
     </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1109,37 +1134,57 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1150,24 +1195,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>